--- a/input/timetable/Экология и природопользование.xlsx
+++ b/input/timetable/Экология и природопользование.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="176">
   <si>
     <t>пара</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -131,9 +134,24 @@
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
+    <t>Кузнецова А.А.</t>
+  </si>
+  <si>
     <t>Безопасность жизнедеятельности (лек 32 ч)</t>
   </si>
   <si>
+    <t>Белощенко Д.В.</t>
+  </si>
+  <si>
+    <t>Болотнов В.П.</t>
+  </si>
+  <si>
+    <t>Самойленко З.А.</t>
+  </si>
+  <si>
+    <t>Бордей Р.Х., Кукуричкин Г.М., Тюрин В.Н.</t>
+  </si>
+  <si>
     <t>Геодезия и картография, п/г 1, А634//</t>
   </si>
   <si>
@@ -143,27 +161,54 @@
     <t>Правоведение (лек 32 ч)</t>
   </si>
   <si>
+    <t>Владимирова Г.Е.</t>
+  </si>
+  <si>
+    <t>Проворова О.В.</t>
+  </si>
+  <si>
     <t>Экология человека (лек), А634</t>
   </si>
   <si>
+    <t>Волохова М.А.</t>
+  </si>
+  <si>
     <t>Экология человека, п/г 1, А634</t>
   </si>
   <si>
     <t>Экология человека, п/г 2, А634</t>
   </si>
   <si>
+    <t>Волохова М.А.;Проворова О.В.</t>
+  </si>
+  <si>
+    <t>Проворова О.В.;Волохова М.А.</t>
+  </si>
+  <si>
+    <t>Кукуричкин Г.М.</t>
+  </si>
+  <si>
     <t>Экологическая химия объектов природной среды, п/г 1, А629</t>
   </si>
   <si>
     <t>Экологическая химия объектов природной среды, п/г 2, А629</t>
   </si>
   <si>
+    <t>Еськов В.В.</t>
+  </si>
+  <si>
+    <t>Тюрин В.Н.</t>
+  </si>
+  <si>
     <t>Дистанционные методы и ГИС в экологии, п/г 1, А509</t>
   </si>
   <si>
     <t>Дистанционные методы и ГИС в экологии, п/г 2, А509</t>
   </si>
   <si>
+    <t>Филатов М.А.</t>
+  </si>
+  <si>
     <t>Биоразнообразие животного мира, п/г 1, А630</t>
   </si>
   <si>
@@ -173,9 +218,21 @@
     <t>304-31</t>
   </si>
   <si>
+    <t>Матковский А.В.</t>
+  </si>
+  <si>
     <t>Основы экономической культуры (лек 32 ч)</t>
   </si>
   <si>
+    <t>Шорникова Е.А./Болотнов В.П.</t>
+  </si>
+  <si>
+    <t>Ханбабаева О.Е.</t>
+  </si>
+  <si>
+    <t>Исаева Т.А.</t>
+  </si>
+  <si>
     <t>Экологические биотехнологии (лек), А634</t>
   </si>
   <si>
@@ -191,10 +248,16 @@
     <t>304-41</t>
   </si>
   <si>
+    <t>Борисенко О.В.</t>
+  </si>
+  <si>
     <t>История России (лек 32 ч)</t>
   </si>
   <si>
     <t>Основы российской государственности (лек 16 ч)</t>
+  </si>
+  <si>
+    <t>Габеркорн А.И.</t>
   </si>
   <si>
     <t>// Геодезия и картография, п/г 2, А634</t>
@@ -299,6 +362,9 @@
     <t>Социальная экология (пр), А634</t>
   </si>
   <si>
+    <t>Шорникова Е.А./Булдин А.Н.</t>
+  </si>
+  <si>
     <t>Экологические биотехнологии, п/г 1, А630// Геохимия, п/г1, А629</t>
   </si>
   <si>
@@ -332,6 +398,15 @@
     <t>02.02.2026-04.04.2026</t>
   </si>
   <si>
+    <t>Шукурова И.В.; Болотнов В.П.</t>
+  </si>
+  <si>
+    <t>Бикмухаметова Л.М.</t>
+  </si>
+  <si>
+    <t>Проворова О.В./Булдин А.Н.; Булдин А.Н./Проворова О.В.</t>
+  </si>
+  <si>
     <t>Экологическая токсикология и биотестирование, п/г 1, А630//</t>
   </si>
   <si>
@@ -344,27 +419,66 @@
     <t>ДВ 05. 02: Ландшафтный дизайн и основы озеленения (лаб), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Кукуричкин Г.М., Наконечный Н.В.</t>
+  </si>
+  <si>
+    <t>Волохова М.А./Проворова О.В.</t>
+  </si>
+  <si>
+    <t>Проворова О.В./Волохова М.А.; Волохова М.А./Проворова О.В.</t>
+  </si>
+  <si>
+    <t>Кукуричкин Г.М., Тюрин В.Н.</t>
+  </si>
+  <si>
+    <t>Кукуричкин Г.М., Тюрин В.Н.; Бикмухаметова Л.М.</t>
+  </si>
+  <si>
+    <t>Белощенко Д.В./Болотнов В.П.</t>
+  </si>
+  <si>
+    <t>Сташкин П.Р.</t>
+  </si>
+  <si>
     <t>Гербарный практикум, п/г 1, А512</t>
   </si>
   <si>
     <t>Гербарный практикум, п/г 2, А512</t>
   </si>
   <si>
+    <t>Кузнецова С.В</t>
+  </si>
+  <si>
+    <t>Проворова О.В.; Умарова М.М..</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 1, У508</t>
   </si>
   <si>
     <t>Иностранный язык, п/г 2, А518</t>
   </si>
   <si>
+    <t>Проворова О.В./Ашарин А.А.</t>
+  </si>
+  <si>
     <t>Основы предпринимательской деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Исаева И.А.</t>
+  </si>
+  <si>
     <t>Экологическая химия объектов природной среды (лек), А634// Правоведение (пр), А503</t>
   </si>
   <si>
     <t>Правоведение (пр), У704// Основы предпринимательской деятельности (пр), К604</t>
   </si>
   <si>
+    <t>Ашарин А.А./Исаева И.А.</t>
+  </si>
+  <si>
+    <t>Кукуричкин Г.М./Харбака В.А.</t>
+  </si>
+  <si>
     <t>Основные типы экосистем Югры (лек), А634// Технологические процессы нефтегазового комплекса (пр), А634</t>
   </si>
   <si>
@@ -374,12 +488,24 @@
     <t>Ландшафтоведение с основами геоэкологии (лек), А634// Гидрометеорология (лек), А634</t>
   </si>
   <si>
+    <t>Джумаева А.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 2, К507</t>
   </si>
   <si>
     <t>Иностранный язык, п/г 1, А501</t>
   </si>
   <si>
+    <t>Сало В.Э. ;Тюрин В.Н.</t>
+  </si>
+  <si>
+    <t>Колосова О.Г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тюрин В.Н.; Сало В.Э. </t>
+  </si>
+  <si>
     <t>Дистанционные методы и ГИС в экологии (лек), А509// Дистанционные методы и ГИС в экологии, п/г 2, А509</t>
   </si>
   <si>
@@ -410,6 +536,12 @@
     <t>//Традиционное природопользование народов севера Западной Сибири (пр), Г224</t>
   </si>
   <si>
+    <t>Сало В.Э.; Филатов М.А., Еськов В.В.</t>
+  </si>
+  <si>
+    <t>Филатов М.А., Еськов В.В.; Сало В.Э.</t>
+  </si>
+  <si>
     <t>Оценка воздействия на окружающую среду, п/г 2, А521</t>
   </si>
   <si>
@@ -419,10 +551,16 @@
     <t>Мониторинг физических факторов (лек), А604</t>
   </si>
   <si>
+    <t>Бикмухаметова Л.М.; Кукуричкин Г.М., Тюрин В.Н.</t>
+  </si>
+  <si>
     <t>Мелиорация и рекультивация земель, п/г 2, А629</t>
   </si>
   <si>
     <t>История России (пр), А539</t>
+  </si>
+  <si>
+    <t>Сердюков Д.В.</t>
   </si>
   <si>
     <t>Основы российской государственности (пр), Г224</t>
@@ -544,7 +682,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -563,6 +701,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -574,7 +718,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -697,6 +841,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1208,6 +1410,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1295,7 +1510,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1331,28 +1546,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1385,13 +1603,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1405,19 +1623,19 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1432,15 +1650,39 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1456,16 +1698,193 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1474,190 +1893,193 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1666,244 +2088,199 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1912,88 +2289,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2317,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2326,10 +2622,11 @@
     <col min="4" max="4" width="19.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2337,15 +2634,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2353,76 +2650,76 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="43">
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="44">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="44" t="s">
-        <v>94</v>
+      <c r="D7" s="136"/>
+      <c r="E7" s="45" t="s">
+        <v>116</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="143" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>0</v>
@@ -2433,345 +2730,414 @@
       <c r="D9" s="18"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="G9" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="125" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="126"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="128"/>
-    </row>
-    <row r="11" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24">
+      <c r="C10" s="100" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="101"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="79" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="132" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" s="134"/>
+      <c r="G11" s="80" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
+        <v>3</v>
+      </c>
+      <c r="C12" s="144"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="107"/>
+      <c r="G12" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="82"/>
-    </row>
-    <row r="12" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="140"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="141"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="80"/>
+    </row>
+    <row r="14" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="29">
+        <v>1</v>
+      </c>
+      <c r="C14" s="156" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="157"/>
+      <c r="E14" s="95" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="96"/>
+      <c r="G14" s="79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
+        <v>2</v>
+      </c>
+      <c r="C15" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="80" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="76"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C16" s="97" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="80" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="72"/>
-    </row>
-    <row r="14" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="28">
+      <c r="C17" s="145"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="80"/>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="29">
         <v>1</v>
       </c>
-      <c r="C14" s="95" t="s">
+      <c r="C18" s="151" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="152"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="153"/>
+      <c r="G18" s="81" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25">
+        <v>2</v>
+      </c>
+      <c r="C19" s="132" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="134"/>
+      <c r="G19" s="82" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="109"/>
+      <c r="E20" s="109"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="64"/>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="30"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="148"/>
+      <c r="D21" s="149"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="65"/>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="29">
+        <v>3</v>
+      </c>
+      <c r="C22" s="111" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="154"/>
+      <c r="E22" s="154"/>
+      <c r="F22" s="155"/>
+      <c r="G22" s="94" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25">
+        <v>4</v>
+      </c>
+      <c r="C23" s="108"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="62"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
+        <v>5</v>
+      </c>
+      <c r="C24" s="108"/>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="80"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="30"/>
+      <c r="B25" s="27">
+        <v>6</v>
+      </c>
+      <c r="C25" s="137"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="66"/>
+    </row>
+    <row r="26" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="29">
+        <v>1</v>
+      </c>
+      <c r="C26" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="112"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="78" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="31"/>
+      <c r="B27" s="25">
+        <v>2</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="80" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="25">
+        <v>3</v>
+      </c>
+      <c r="C28" s="104"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="107"/>
+      <c r="G28" s="80" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="32"/>
+      <c r="B29" s="27">
+        <v>4</v>
+      </c>
+      <c r="C29" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="123"/>
+      <c r="G29" s="83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="29">
+        <v>1</v>
+      </c>
+      <c r="C30" s="127"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="75"/>
+    </row>
+    <row r="31" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="34"/>
+      <c r="B31" s="25">
+        <v>2</v>
+      </c>
+      <c r="C31" s="132"/>
+      <c r="D31" s="133"/>
+      <c r="E31" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="134"/>
+      <c r="G31" s="80" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="35"/>
+      <c r="B32" s="27">
+        <v>3</v>
+      </c>
+      <c r="C32" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="131"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="83" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="36"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="68"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="38"/>
+      <c r="B34" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="111" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="114"/>
+      <c r="G34" s="78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="39"/>
+      <c r="B35" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="118" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="96"/>
-      <c r="E14" s="123" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="124"/>
-    </row>
-    <row r="15" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24">
-        <v>2</v>
-      </c>
-      <c r="C15" s="120" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
-    </row>
-    <row r="16" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
-        <v>3</v>
-      </c>
-      <c r="C16" s="120" t="s">
-        <v>128</v>
-      </c>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="122"/>
-    </row>
-    <row r="17" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
-        <v>4</v>
-      </c>
-      <c r="C17" s="77"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="79"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="28">
-        <v>1</v>
-      </c>
-      <c r="C18" s="89" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="90"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="91"/>
-    </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24">
-        <v>2</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="82"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="85"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="29"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="88"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="28">
-        <v>3</v>
-      </c>
-      <c r="C22" s="92" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="94"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24">
-        <v>4</v>
-      </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="85"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24">
-        <v>5</v>
-      </c>
-      <c r="C24" s="83"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="85"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="29"/>
-      <c r="B25" s="26">
-        <v>6</v>
-      </c>
-      <c r="C25" s="67"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69"/>
-    </row>
-    <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="28">
-        <v>1</v>
-      </c>
-      <c r="C26" s="92" t="s">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="39"/>
+      <c r="B36" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="118"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="115"/>
-    </row>
-    <row r="27" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="30"/>
-      <c r="B27" s="24">
-        <v>2</v>
-      </c>
-      <c r="C27" s="120" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="122"/>
-    </row>
-    <row r="28" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24">
-        <v>3</v>
-      </c>
-      <c r="C28" s="116"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="75" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="76"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="31"/>
-      <c r="B29" s="26">
-        <v>4</v>
-      </c>
-      <c r="C29" s="103" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="104"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="105"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="28">
-        <v>1</v>
-      </c>
-      <c r="C30" s="109"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="111"/>
-    </row>
-    <row r="31" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="33"/>
-      <c r="B31" s="24">
-        <v>2</v>
-      </c>
-      <c r="C31" s="80"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="82"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="34"/>
-      <c r="B32" s="26">
-        <v>3</v>
-      </c>
-      <c r="C32" s="112" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="99"/>
-    </row>
-    <row r="33" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="108"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="37"/>
-      <c r="B34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="92" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="114"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="115"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="38"/>
-      <c r="B35" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="101"/>
-      <c r="E35" s="101"/>
-      <c r="F35" s="102"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="100" t="s">
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="84" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="41"/>
+      <c r="B37" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="115" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="101"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="102"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="40"/>
-      <c r="B37" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="97" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="99"/>
-    </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>15</v>
       </c>
@@ -2781,28 +3147,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C34:F34"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C13:F13"/>
@@ -2819,6 +3163,28 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2849,7 +3215,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2858,10 +3224,11 @@
     <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2869,15 +3236,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2885,76 +3252,76 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="43">
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="44">
         <v>2</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="44" t="s">
-        <v>54</v>
+      <c r="D7" s="136"/>
+      <c r="E7" s="45" t="s">
+        <v>73</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="143" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>0</v>
@@ -2965,323 +3332,382 @@
       <c r="D9" s="18"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="G9" s="57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="131" t="s">
+      <c r="C10" s="202" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="79" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
+        <v>2</v>
+      </c>
+      <c r="C11" s="205"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="62"/>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="163" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="164"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="66"/>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="29">
+        <v>2</v>
+      </c>
+      <c r="C13" s="111"/>
+      <c r="D13" s="154"/>
+      <c r="E13" s="154"/>
+      <c r="F13" s="155"/>
+      <c r="G13" s="80"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25">
+        <v>3</v>
+      </c>
+      <c r="C14" s="97" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="133"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24">
+    </row>
+    <row r="15" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
+        <v>4</v>
+      </c>
+      <c r="C15" s="166" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="167"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="80" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="30"/>
+      <c r="B16" s="27">
+        <v>5</v>
+      </c>
+      <c r="C16" s="158" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="159"/>
+      <c r="E16" s="160" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="161"/>
+      <c r="G16" s="83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="29">
+        <v>1</v>
+      </c>
+      <c r="C17" s="193" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="78" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="135"/>
-      <c r="F11" s="136"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C18" s="97" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="172"/>
+      <c r="E18" s="173" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="99"/>
+      <c r="G18" s="80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="164" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="166"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="28">
+      <c r="C19" s="132" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="134"/>
+      <c r="G19" s="80" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
+        <v>4</v>
+      </c>
+      <c r="C20" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="175"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="176"/>
+      <c r="G20" s="80" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="29">
+        <v>1</v>
+      </c>
+      <c r="C21" s="199"/>
+      <c r="D21" s="200"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="201"/>
+      <c r="G21" s="78"/>
+    </row>
+    <row r="22" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25">
         <v>2</v>
       </c>
-      <c r="C13" s="92"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24">
+      <c r="C22" s="108"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="133" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="134"/>
+      <c r="G22" s="84" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="30"/>
+      <c r="B23" s="27">
         <v>3</v>
       </c>
-      <c r="C14" s="120" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
-    </row>
-    <row r="15" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24">
+      <c r="C23" s="196" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="197"/>
+      <c r="E23" s="197"/>
+      <c r="F23" s="198"/>
+      <c r="G23" s="62"/>
+    </row>
+    <row r="24" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="29">
+        <v>2</v>
+      </c>
+      <c r="C24" s="111" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="154"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="O24" s="70"/>
+    </row>
+    <row r="25" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="31"/>
+      <c r="B25" s="25">
+        <v>3</v>
+      </c>
+      <c r="C25" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="172"/>
+      <c r="E25" s="173" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="99"/>
+      <c r="G25" s="80" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="31"/>
+      <c r="B26" s="25">
         <v>4</v>
       </c>
-      <c r="C15" s="167" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="169"/>
-    </row>
-    <row r="16" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="29"/>
-      <c r="B16" s="26">
+      <c r="C26" s="132" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="133"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="80" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="32"/>
+      <c r="B27" s="27">
         <v>5</v>
       </c>
-      <c r="C16" s="159" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="160"/>
-      <c r="E16" s="161" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="162"/>
-    </row>
-    <row r="17" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="28">
+      <c r="C27" s="186"/>
+      <c r="D27" s="187"/>
+      <c r="E27" s="187"/>
+      <c r="F27" s="188"/>
+      <c r="G27" s="66"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A28" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="23">
         <v>1</v>
       </c>
-      <c r="C17" s="137" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="139"/>
-    </row>
-    <row r="18" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24">
+      <c r="C28" s="189"/>
+      <c r="D28" s="190"/>
+      <c r="E28" s="190"/>
+      <c r="F28" s="191"/>
+      <c r="G28" s="76"/>
+    </row>
+    <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="25">
         <v>2</v>
       </c>
-      <c r="C18" s="120" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="129"/>
-      <c r="E18" s="130" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="122"/>
-    </row>
-    <row r="19" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24">
+      <c r="C29" s="177" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="178"/>
+      <c r="E29" s="178"/>
+      <c r="F29" s="179"/>
+      <c r="G29" s="80" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="69">
         <v>3</v>
       </c>
-      <c r="C19" s="80" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" s="82"/>
-    </row>
-    <row r="20" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24">
-        <v>4</v>
-      </c>
-      <c r="C20" s="173" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="174"/>
-      <c r="E20" s="174"/>
-      <c r="F20" s="175"/>
-    </row>
-    <row r="21" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="28">
-        <v>1</v>
-      </c>
-      <c r="C21" s="143"/>
-      <c r="D21" s="144"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="145"/>
-    </row>
-    <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24">
-        <v>2</v>
-      </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="82"/>
-    </row>
-    <row r="23" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="29"/>
-      <c r="B23" s="26">
-        <v>3</v>
-      </c>
-      <c r="C23" s="140" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="141"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="142"/>
-    </row>
-    <row r="24" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="28">
-        <v>2</v>
-      </c>
-      <c r="C24" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="94"/>
-      <c r="N24" s="61"/>
-    </row>
-    <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="30"/>
-      <c r="B25" s="24">
-        <v>3</v>
-      </c>
-      <c r="C25" s="120" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" s="129"/>
-      <c r="E25" s="130" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="122"/>
-    </row>
-    <row r="26" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30"/>
-      <c r="B26" s="24">
-        <v>4</v>
-      </c>
-      <c r="C26" s="80" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="81"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="85"/>
-    </row>
-    <row r="27" spans="1:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="31"/>
-      <c r="B27" s="26">
-        <v>5</v>
-      </c>
-      <c r="C27" s="152"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="154"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A28" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="22">
-        <v>1</v>
-      </c>
-      <c r="C28" s="155"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="156"/>
-      <c r="F28" s="157"/>
-    </row>
-    <row r="29" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="33"/>
-      <c r="B29" s="24">
-        <v>2</v>
-      </c>
-      <c r="C29" s="176" t="s">
+      <c r="C30" s="169" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="170"/>
+      <c r="E30" s="171" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="165"/>
+      <c r="G30" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="177"/>
-      <c r="E29" s="177"/>
-      <c r="F29" s="178"/>
-    </row>
-    <row r="30" spans="1:14" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="38"/>
-      <c r="B30" s="60">
-        <v>3</v>
-      </c>
-      <c r="C30" s="170" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="171"/>
-      <c r="E30" s="172" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="166"/>
-    </row>
-    <row r="31" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="46"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="147"/>
-      <c r="E31" s="147"/>
-      <c r="F31" s="148"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
-      <c r="B32" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="158" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="115"/>
-    </row>
-    <row r="33" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40"/>
-      <c r="B33" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="149" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="150"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="151"/>
-    </row>
-    <row r="34" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="163" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="163"/>
-      <c r="C34" s="163"/>
-      <c r="D34" s="163"/>
-      <c r="E34" s="163"/>
-      <c r="F34" s="163"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="47"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="181"/>
+      <c r="E31" s="181"/>
+      <c r="F31" s="182"/>
+      <c r="G31" s="77"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A32" s="49"/>
+      <c r="B32" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="192" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="135"/>
+      <c r="E32" s="135"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="88" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="41"/>
+      <c r="B33" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="183" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="184"/>
+      <c r="E33" s="184"/>
+      <c r="F33" s="185"/>
+      <c r="G33" s="89" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="162" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="162"/>
+      <c r="C34" s="162"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="162"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>15</v>
       </c>
@@ -3291,6 +3717,26 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C26:D26"/>
@@ -3305,26 +3751,6 @@
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3355,7 +3781,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3363,10 +3789,11 @@
     <col min="3" max="3" width="22.140625" style="2" customWidth="1"/>
     <col min="4" max="5" width="21.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3374,15 +3801,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3390,76 +3817,76 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="43">
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="44">
         <v>3</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="44" t="s">
-        <v>48</v>
+      <c r="D7" s="136"/>
+      <c r="E7" s="45" t="s">
+        <v>63</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="143" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+    </row>
+    <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>0</v>
@@ -3470,332 +3897,397 @@
       <c r="D9" s="18"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="G9" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="23">
         <v>2</v>
       </c>
-      <c r="C10" s="137" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="138"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="139"/>
-    </row>
-    <row r="11" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24">
+      <c r="C10" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="194"/>
+      <c r="E10" s="194"/>
+      <c r="F10" s="195"/>
+      <c r="G10" s="79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <v>3</v>
       </c>
-      <c r="C11" s="77" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="79"/>
-    </row>
-    <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="145" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="80" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>4</v>
       </c>
-      <c r="C12" s="120" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="122"/>
-      <c r="L12" s="64"/>
-    </row>
-    <row r="13" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="50"/>
-      <c r="B13" s="39">
+      <c r="C12" s="97" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="82" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="73"/>
+    </row>
+    <row r="13" spans="1:13" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="51"/>
+      <c r="B13" s="40">
         <v>5</v>
       </c>
-      <c r="C13" s="192"/>
-      <c r="D13" s="193"/>
-      <c r="E13" s="193"/>
-      <c r="F13" s="194"/>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="28" t="s">
+      <c r="C13" s="233"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="84"/>
+    </row>
+    <row r="14" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="211" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+      <c r="F14" s="213"/>
+      <c r="G14" s="75"/>
+    </row>
+    <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
+        <v>4</v>
+      </c>
+      <c r="C15" s="230" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="232"/>
+      <c r="G15" s="80" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
+        <v>5</v>
+      </c>
+      <c r="C16" s="230" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="231"/>
+      <c r="E16" s="231" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="232"/>
+      <c r="G16" s="80" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="30"/>
+      <c r="B17" s="27">
+        <v>6</v>
+      </c>
+      <c r="C17" s="130"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="229"/>
+      <c r="G17" s="83"/>
+    </row>
+    <row r="18" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="29">
+        <v>1</v>
+      </c>
+      <c r="C18" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" s="154"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="155"/>
+      <c r="G18" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="O18" s="74"/>
+    </row>
+    <row r="19" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="24"/>
+      <c r="B19" s="23">
+        <v>2</v>
+      </c>
+      <c r="C19" s="132" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="133"/>
+      <c r="E19" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="99"/>
+      <c r="G19" s="85" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
+        <v>3</v>
+      </c>
+      <c r="C20" s="132" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="133"/>
+      <c r="E20" s="173" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="99"/>
+      <c r="G20" s="80" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>4</v>
+      </c>
+      <c r="C21" s="158" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="159"/>
+      <c r="E21" s="208"/>
+      <c r="F21" s="209"/>
+      <c r="G21" s="80" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="29">
+        <v>2</v>
+      </c>
+      <c r="C22" s="214" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="215"/>
+      <c r="E22" s="215"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="78" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="69.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25">
+        <v>3</v>
+      </c>
+      <c r="C23" s="177" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="178"/>
+      <c r="E23" s="178" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" s="179"/>
+      <c r="G23" s="84" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
+        <v>4</v>
+      </c>
+      <c r="C24" s="177" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="178"/>
+      <c r="E24" s="178" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="179"/>
+      <c r="G24" s="84" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="30"/>
+      <c r="B25" s="27">
+        <v>5</v>
+      </c>
+      <c r="C25" s="236"/>
+      <c r="D25" s="237"/>
+      <c r="E25" s="237"/>
+      <c r="F25" s="238"/>
+      <c r="G25" s="66"/>
+    </row>
+    <row r="26" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="29">
+        <v>3</v>
+      </c>
+      <c r="C26" s="211" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="213"/>
+      <c r="G26" s="85" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="31"/>
+      <c r="B27" s="25">
+        <v>5</v>
+      </c>
+      <c r="C27" s="166" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="167"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="168"/>
+      <c r="G27" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="195" t="s">
+    </row>
+    <row r="28" spans="1:15" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="52"/>
+      <c r="B28" s="40">
+        <v>6</v>
+      </c>
+      <c r="C28" s="223" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="224"/>
+      <c r="E28" s="224"/>
+      <c r="F28" s="225"/>
+      <c r="G28" s="84" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="29">
+        <v>2</v>
+      </c>
+      <c r="C29" s="220" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="221"/>
+      <c r="E29" s="221"/>
+      <c r="F29" s="222"/>
+      <c r="G29" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="196"/>
-      <c r="E14" s="196"/>
-      <c r="F14" s="197"/>
-    </row>
-    <row r="15" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24">
+    </row>
+    <row r="30" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="34"/>
+      <c r="B30" s="25">
         <v>4</v>
       </c>
-      <c r="C15" s="189" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="190"/>
-      <c r="E15" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="191"/>
-    </row>
-    <row r="16" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C30" s="132" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="133"/>
+      <c r="E30" s="133"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="80" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="35"/>
+      <c r="B31" s="27">
         <v>5</v>
       </c>
-      <c r="C16" s="189" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="190"/>
-      <c r="E16" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="191"/>
-    </row>
-    <row r="17" spans="1:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="29"/>
-      <c r="B17" s="26">
-        <v>6</v>
-      </c>
-      <c r="C17" s="112"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="188"/>
-    </row>
-    <row r="18" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="28">
-        <v>1</v>
-      </c>
-      <c r="C18" s="92" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="94"/>
-      <c r="N18" s="65"/>
-    </row>
-    <row r="19" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="23"/>
-      <c r="B19" s="22">
-        <v>2</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="130" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="122"/>
-    </row>
-    <row r="20" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24">
-        <v>3</v>
-      </c>
-      <c r="C20" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="130" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="122"/>
-    </row>
-    <row r="21" spans="1:14" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
-        <v>4</v>
-      </c>
-      <c r="C21" s="159" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="160"/>
-      <c r="E21" s="198"/>
-      <c r="F21" s="199"/>
-    </row>
-    <row r="22" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="28">
-        <v>2</v>
-      </c>
-      <c r="C22" s="201" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="203"/>
-    </row>
-    <row r="23" spans="1:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24">
-        <v>3</v>
-      </c>
-      <c r="C23" s="176" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="177"/>
-      <c r="E23" s="177" t="s">
-        <v>119</v>
-      </c>
-      <c r="F23" s="178"/>
-    </row>
-    <row r="24" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24">
-        <v>4</v>
-      </c>
-      <c r="C24" s="176" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="177"/>
-      <c r="E24" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="178"/>
-    </row>
-    <row r="25" spans="1:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="29"/>
-      <c r="B25" s="26">
-        <v>5</v>
-      </c>
-      <c r="C25" s="179"/>
-      <c r="D25" s="180"/>
-      <c r="E25" s="180"/>
-      <c r="F25" s="181"/>
-    </row>
-    <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="28">
-        <v>3</v>
-      </c>
-      <c r="C26" s="195" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="196"/>
-      <c r="E26" s="196"/>
-      <c r="F26" s="197"/>
-    </row>
-    <row r="27" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="30"/>
-      <c r="B27" s="24">
-        <v>5</v>
-      </c>
-      <c r="C27" s="167" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="168"/>
-      <c r="E27" s="168"/>
-      <c r="F27" s="169"/>
-    </row>
-    <row r="28" spans="1:14" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="51"/>
-      <c r="B28" s="39">
-        <v>6</v>
-      </c>
-      <c r="C28" s="182" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="183"/>
-      <c r="E28" s="183"/>
-      <c r="F28" s="184"/>
-    </row>
-    <row r="29" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="28">
-        <v>2</v>
-      </c>
-      <c r="C29" s="207" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" s="208"/>
-      <c r="E29" s="208"/>
-      <c r="F29" s="209"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="33"/>
-      <c r="B30" s="24">
-        <v>4</v>
-      </c>
-      <c r="C30" s="80" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="82"/>
-    </row>
-    <row r="31" spans="1:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="34"/>
-      <c r="B31" s="26">
-        <v>5</v>
-      </c>
-      <c r="C31" s="97" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="99"/>
-    </row>
-    <row r="32" spans="1:14" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="58"/>
-      <c r="B32" s="59"/>
-      <c r="C32" s="185"/>
-      <c r="D32" s="186"/>
-      <c r="E32" s="186"/>
-      <c r="F32" s="187"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="56"/>
-      <c r="B33" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="204" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="205"/>
-      <c r="E33" s="205"/>
-      <c r="F33" s="206"/>
-    </row>
-    <row r="34" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="62" t="s">
-        <v>69</v>
-      </c>
-      <c r="B34" s="63"/>
-      <c r="C34" s="200" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="200"/>
-      <c r="E34" s="200"/>
-      <c r="F34" s="200"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C31" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="80" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="60"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="226"/>
+      <c r="D32" s="227"/>
+      <c r="E32" s="227"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="67"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="58"/>
+      <c r="B33" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="217" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="218"/>
+      <c r="E33" s="218"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="90" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="72"/>
+      <c r="C34" s="210" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="210"/>
+      <c r="E34" s="210"/>
+      <c r="F34" s="210"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>15</v>
       </c>
@@ -3805,6 +4297,26 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E21:F21"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:F19"/>
@@ -3819,26 +4331,6 @@
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3869,7 +4361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3878,10 +4370,11 @@
     <col min="4" max="4" width="19.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3889,15 +4382,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3905,86 +4398,86 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="43">
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="44">
         <v>4</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="44" t="s">
-        <v>30</v>
+      <c r="D7" s="136"/>
+      <c r="E7" s="45" t="s">
+        <v>31</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="55"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="55"/>
+      <c r="E8" s="56"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="55"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+      <c r="C9" s="143" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="143"/>
+      <c r="E9" s="56"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -3995,297 +4488,349 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="G10" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="23">
         <v>2</v>
       </c>
-      <c r="C11" s="210" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="211"/>
-      <c r="E11" s="211"/>
-      <c r="F11" s="212"/>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="266" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="268"/>
+      <c r="G11" s="93" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="74" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="76"/>
-    </row>
-    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C12" s="144" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="80" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="216" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="217"/>
-      <c r="E13" s="217" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="218"/>
-    </row>
-    <row r="14" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="272" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="273"/>
+      <c r="E13" s="273" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="274"/>
+      <c r="G13" s="91" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="213" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="215"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="C14" s="269" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="270"/>
+      <c r="E14" s="270" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="271"/>
+      <c r="G14" s="92" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="29">
         <v>3</v>
       </c>
-      <c r="C15" s="210"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
-      <c r="F15" s="212"/>
-    </row>
-    <row r="16" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="266"/>
+      <c r="D15" s="267"/>
+      <c r="E15" s="267"/>
+      <c r="F15" s="268"/>
+      <c r="G15" s="86"/>
+    </row>
+    <row r="16" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>4</v>
       </c>
-      <c r="C16" s="74" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="75"/>
-      <c r="E16" s="75"/>
-      <c r="F16" s="76"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="C16" s="144" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="80" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>5</v>
       </c>
-      <c r="C17" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="76"/>
-    </row>
-    <row r="18" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="26">
+      <c r="C17" s="144" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="80" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="27">
         <v>6</v>
       </c>
-      <c r="C18" s="140"/>
-      <c r="D18" s="141"/>
-      <c r="E18" s="141" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="142"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="28">
+      <c r="C18" s="196"/>
+      <c r="D18" s="197"/>
+      <c r="E18" s="197" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="198"/>
+      <c r="G18" s="80" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="29">
         <v>2</v>
       </c>
-      <c r="C19" s="231" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="232"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="233"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="22">
+      <c r="C19" s="239" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="240"/>
+      <c r="E19" s="240"/>
+      <c r="F19" s="241"/>
+      <c r="G19" s="78"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23">
         <v>3</v>
       </c>
-      <c r="C20" s="243"/>
-      <c r="D20" s="244"/>
-      <c r="E20" s="244"/>
-      <c r="F20" s="245"/>
-    </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
+      <c r="C20" s="263"/>
+      <c r="D20" s="264"/>
+      <c r="E20" s="264"/>
+      <c r="F20" s="265"/>
+      <c r="G20" s="85"/>
+    </row>
+    <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <v>4</v>
       </c>
-      <c r="C21" s="228"/>
-      <c r="D21" s="229"/>
-      <c r="E21" s="229"/>
-      <c r="F21" s="230"/>
-    </row>
-    <row r="22" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26">
+      <c r="C21" s="257"/>
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="259"/>
+      <c r="G21" s="80"/>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
         <v>5</v>
       </c>
-      <c r="C22" s="179"/>
-      <c r="D22" s="180"/>
-      <c r="E22" s="180"/>
-      <c r="F22" s="181"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="28">
+      <c r="C22" s="236"/>
+      <c r="D22" s="237"/>
+      <c r="E22" s="237"/>
+      <c r="F22" s="238"/>
+      <c r="G22" s="84"/>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="29">
         <v>2</v>
       </c>
-      <c r="C23" s="240"/>
-      <c r="D23" s="241"/>
-      <c r="E23" s="241"/>
-      <c r="F23" s="242"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="22">
+      <c r="C23" s="260"/>
+      <c r="D23" s="261"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="262"/>
+      <c r="G23" s="78"/>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="23">
         <v>3</v>
       </c>
-      <c r="C24" s="237"/>
-      <c r="D24" s="238"/>
-      <c r="E24" s="238"/>
-      <c r="F24" s="239"/>
-    </row>
-    <row r="25" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
+      <c r="C24" s="245"/>
+      <c r="D24" s="246"/>
+      <c r="E24" s="246"/>
+      <c r="F24" s="247"/>
+      <c r="G24" s="80"/>
+    </row>
+    <row r="25" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <v>4</v>
       </c>
-      <c r="C25" s="120" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="122"/>
-    </row>
-    <row r="26" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26">
+      <c r="C25" s="97" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="80" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27">
         <v>5</v>
       </c>
-      <c r="C26" s="234" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="236"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="28">
+      <c r="C26" s="242" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="243"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="84" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="29">
         <v>3</v>
       </c>
-      <c r="C27" s="231" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="232"/>
-      <c r="E27" s="232"/>
-      <c r="F27" s="233"/>
-    </row>
-    <row r="28" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24">
+      <c r="C27" s="239" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="240"/>
+      <c r="E27" s="240"/>
+      <c r="F27" s="241"/>
+      <c r="G27" s="86" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="25">
         <v>4</v>
       </c>
-      <c r="C28" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="81"/>
-      <c r="E28" s="81" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" s="82"/>
-    </row>
-    <row r="29" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="24">
+      <c r="C28" s="132" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="133"/>
+      <c r="E28" s="133" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="134"/>
+      <c r="G28" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="25">
         <v>5</v>
       </c>
-      <c r="C29" s="189" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="190"/>
-      <c r="E29" s="190" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" s="191"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="26">
+      <c r="C29" s="230" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="231"/>
+      <c r="E29" s="231" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" s="232"/>
+      <c r="G29" s="87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="32"/>
+      <c r="B30" s="27">
         <v>6</v>
       </c>
-      <c r="C30" s="222" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="223"/>
-      <c r="E30" s="223"/>
-      <c r="F30" s="224"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="22">
+      <c r="C30" s="251" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="252"/>
+      <c r="E30" s="252"/>
+      <c r="F30" s="253"/>
+      <c r="G30" s="87" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="23">
         <v>1</v>
       </c>
-      <c r="C31" s="225" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="227"/>
-    </row>
-    <row r="32" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="33"/>
-      <c r="B32" s="24">
+      <c r="C31" s="254" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="256"/>
+      <c r="G31" s="63"/>
+    </row>
+    <row r="32" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="34"/>
+      <c r="B32" s="25">
         <v>2</v>
       </c>
-      <c r="C32" s="228"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="230"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40"/>
-      <c r="B33" s="52">
+      <c r="C32" s="257"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="258"/>
+      <c r="F32" s="259"/>
+      <c r="G32" s="64"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="41"/>
+      <c r="B33" s="53">
         <v>3</v>
       </c>
-      <c r="C33" s="219"/>
-      <c r="D33" s="220"/>
-      <c r="E33" s="220"/>
-      <c r="F33" s="221"/>
-    </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="248"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="250"/>
+      <c r="G33" s="65"/>
+    </row>
+    <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>15</v>
       </c>
@@ -4295,23 +4840,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C9:D9"/>
@@ -4326,6 +4854,23 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C20:F20"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
